--- a/src/test/resources/testdata/TestData.xlsx
+++ b/src/test/resources/testdata/TestData.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30110"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30121"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HITENDRA VERMA\eclipse-workspace\OrangeHRMProject\src\test\resources\testdata\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{13B0EAF8-6190-4E7D-AA9F-AEF4F83A405A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{D43E62EC-7C86-40F2-A295-BA02752E8E78}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" firstSheet="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="validLoginData" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="9">
   <si>
     <t>username</t>
   </si>
@@ -46,16 +46,13 @@
     <t>password</t>
   </si>
   <si>
-    <t>admin</t>
-  </si>
-  <si>
-    <t>Cocoy123!@#</t>
+    <t>Admin</t>
+  </si>
+  <si>
+    <t>admin123</t>
   </si>
   <si>
     <t>admin1</t>
-  </si>
-  <si>
-    <t>admin123</t>
   </si>
   <si>
     <t>emp_id</t>
@@ -441,7 +438,7 @@
         <v>4</v>
       </c>
       <c r="B2" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
   </sheetData>
@@ -459,10 +456,10 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B1" t="s">
         <v>6</v>
-      </c>
-      <c r="B1" t="s">
-        <v>7</v>
       </c>
     </row>
     <row r="2" spans="1:2">
@@ -470,7 +467,7 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -478,7 +475,7 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>
